--- a/tools/config-xlsx/equip.xlsx
+++ b/tools/config-xlsx/equip.xlsx
@@ -6,6 +6,7 @@
     <sheet name="Qualities" sheetId="1" r:id="rId1"/>
     <sheet name="SlotBonuses" sheetId="2" r:id="rId2"/>
     <sheet name="Affixes" sheetId="3" r:id="rId3"/>
+    <sheet name="LevelScaling" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -776,4 +777,39 @@
     <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>growthPerLevel</v>
+      </c>
+      <c r="B2">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>maxLevel</v>
+      </c>
+      <c r="B3">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/tools/config-xlsx/equip.xlsx
+++ b/tools/config-xlsx/equip.xlsx
@@ -552,7 +552,7 @@
         <v>atk</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -574,7 +574,7 @@
         <v>hp</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
@@ -596,7 +596,7 @@
         <v>hp</v>
       </c>
       <c r="C6">
-        <v>60</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
@@ -629,7 +629,7 @@
         <v>hp</v>
       </c>
       <c r="C9">
-        <v>45</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10">
@@ -689,7 +689,7 @@
         <v>hp</v>
       </c>
       <c r="B2">
-        <v>28</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3">
@@ -697,7 +697,7 @@
         <v>atk</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">

--- a/tools/config-xlsx/equip.xlsx
+++ b/tools/config-xlsx/equip.xlsx
@@ -552,7 +552,7 @@
         <v>atk</v>
       </c>
       <c r="C2">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -574,7 +574,7 @@
         <v>hp</v>
       </c>
       <c r="C4">
-        <v>200</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5">
@@ -585,7 +585,7 @@
         <v>def</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -596,7 +596,7 @@
         <v>hp</v>
       </c>
       <c r="C6">
-        <v>300</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7">
@@ -607,7 +607,7 @@
         <v>def</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         <v>hp</v>
       </c>
       <c r="C9">
-        <v>225</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -674,7 +674,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -689,7 +689,7 @@
         <v>hp</v>
       </c>
       <c r="B2">
-        <v>140</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3">
@@ -697,7 +697,7 @@
         <v>atk</v>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -705,7 +705,7 @@
         <v>def</v>
       </c>
       <c r="B4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -772,9 +772,73 @@
         <v>0.01</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>hpPct</v>
+      </c>
+      <c r="B13">
+        <v>0.0389</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>atkPct</v>
+      </c>
+      <c r="B14">
+        <v>0.0389</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>defPct</v>
+      </c>
+      <c r="B15">
+        <v>0.0389</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>moveSpeed</v>
+      </c>
+      <c r="B16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>moveSpeedPct</v>
+      </c>
+      <c r="B17">
+        <v>0.0389</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>skillHaste</v>
+      </c>
+      <c r="B18">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>basicDmgBonus</v>
+      </c>
+      <c r="B19">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>skillDmgBonus</v>
+      </c>
+      <c r="B20">
+        <v>0.04</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B20"/>
   </ignoredErrors>
 </worksheet>
 </file>
